--- a/AMZN Model.xlsx
+++ b/AMZN Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA22530-9D23-4728-B548-511E235F2930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FB04BC-66CF-427D-8932-1DD23F902BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7116" yWindow="156" windowWidth="32016" windowHeight="15936" xr2:uid="{15DD2EF7-3D38-48BE-91C3-905AF47E584F}"/>
+    <workbookView xWindow="28404" yWindow="1764" windowWidth="28056" windowHeight="14364" activeTab="1" xr2:uid="{15DD2EF7-3D38-48BE-91C3-905AF47E584F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="135">
   <si>
     <t>Company Overview</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>EBITDA AWS</t>
   </si>
 </sst>
 </file>
@@ -454,11 +457,17 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -639,68 +648,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -719,101 +728,103 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
     <xf numFmtId="3" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="37" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="37" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4398,7 +4409,7 @@
         <v>107556</v>
       </c>
       <c r="J34" s="55">
-        <v>127873</v>
+        <v>128725</v>
       </c>
       <c r="K34" s="68">
         <v>154576</v>
@@ -4443,11 +4454,11 @@
       </c>
       <c r="J35" s="59">
         <f t="shared" ref="J35" si="59">J34/I34-1</f>
-        <v>0.18889694670683177</v>
+        <v>0.19681840157685304</v>
       </c>
       <c r="K35" s="59">
         <f t="shared" ref="K35" si="60">K34/J34-1</f>
-        <v>0.20882438043996787</v>
+        <v>0.20082346086618763</v>
       </c>
       <c r="L35" s="59">
         <f t="shared" ref="L35" si="61">L34/K34-1</f>
@@ -4598,32 +4609,112 @@
       <c r="Q41" s="68"/>
     </row>
     <row r="42" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="68"/>
-      <c r="M42" s="68"/>
-      <c r="N42" s="68"/>
-      <c r="O42" s="68"/>
+      <c r="B42" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="55">
+        <v>13531</v>
+      </c>
+      <c r="F42" s="55">
+        <v>18532</v>
+      </c>
+      <c r="G42" s="55">
+        <v>22841</v>
+      </c>
+      <c r="H42" s="55">
+        <v>24631</v>
+      </c>
+      <c r="I42" s="55">
+        <v>39834</v>
+      </c>
+      <c r="J42" s="55">
+        <v>45606</v>
+      </c>
+      <c r="K42" s="68">
+        <v>52644.7</v>
+      </c>
+      <c r="L42" s="68">
+        <v>63144.4</v>
+      </c>
+      <c r="M42" s="68">
+        <v>75972.3</v>
+      </c>
+      <c r="N42" s="68">
+        <v>90809</v>
+      </c>
+      <c r="O42" s="68">
+        <v>106958</v>
+      </c>
       <c r="P42" s="68"/>
       <c r="Q42" s="68"/>
     </row>
     <row r="43" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="68"/>
-      <c r="N43" s="68"/>
-      <c r="O43" s="68"/>
+      <c r="B43" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="92">
+        <f>E42/E34</f>
+        <v>0.29823672029975756</v>
+      </c>
+      <c r="F43" s="92">
+        <f t="shared" ref="F43:O43" si="65">F42/F34</f>
+        <v>0.29793254236198191</v>
+      </c>
+      <c r="G43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.28517029564522572</v>
+      </c>
+      <c r="H43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.27139504390845887</v>
+      </c>
+      <c r="I43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.37035590762021642</v>
+      </c>
+      <c r="J43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.35429015342785009</v>
+      </c>
+      <c r="K43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.34057486285063654</v>
+      </c>
+      <c r="L43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.33794709040016702</v>
+      </c>
+      <c r="M43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.33708686257370918</v>
+      </c>
+      <c r="N43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.33854395788751612</v>
+      </c>
+      <c r="O43" s="92">
+        <f t="shared" si="65"/>
+        <v>0.32865557812322355</v>
+      </c>
       <c r="P43" s="68"/>
       <c r="Q43" s="68"/>
+    </row>
+    <row r="45" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="J45" s="55">
+        <v>77003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J46" s="92">
+        <f>J45/K34</f>
+        <v>0.4981562467653452</v>
+      </c>
     </row>
     <row r="65" spans="17:26" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="S65" s="67"/>
@@ -4832,7 +4923,7 @@
       <c r="Z84" s="76"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
